--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,6 +804,130 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120249280</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57679</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mölleskogen, Lången-området, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>511290</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6578077</v>
+      </c>
+      <c r="S3" t="n">
+        <v>100</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hovsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>120249280</v>
       </c>
       <c r="B3" t="n">
-        <v>57679</v>
+        <v>57689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>126842634</v>
       </c>
       <c r="B4" t="n">
-        <v>57939</v>
+        <v>57943</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,123 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128548833</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56611</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mölleskogen, Lången-området, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>511290</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6578077</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hovsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>128548833</v>
       </c>
       <c r="B5" t="n">
-        <v>56611</v>
+        <v>56615</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>128548833</v>
       </c>
       <c r="B5" t="n">
-        <v>56615</v>
+        <v>56642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>128548833</v>
       </c>
       <c r="B5" t="n">
-        <v>56642</v>
+        <v>56645</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>128548833</v>
       </c>
       <c r="B5" t="n">
-        <v>56645</v>
+        <v>56648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>126842634</v>
       </c>
       <c r="B4" t="n">
-        <v>57943</v>
+        <v>57939</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>87069564</v>
       </c>
       <c r="B2" t="n">
-        <v>56286</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,7 +695,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Accipiter gentilis</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -735,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>511289.5239037495</v>
+        <v>511290</v>
       </c>
       <c r="R2" t="n">
-        <v>6578077.137746724</v>
+        <v>6578077</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -807,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120249280</v>
+        <v>111225026</v>
       </c>
       <c r="B3" t="n">
-        <v>57701</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102626</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +836,14 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -889,22 +883,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2023-07-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +918,7 @@
         <v>126842634</v>
       </c>
       <c r="B4" t="n">
-        <v>57943</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128548833</v>
+        <v>110839532</v>
       </c>
       <c r="B5" t="n">
-        <v>56648</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208257</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1083,10 +1067,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,22 +1111,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2023-07-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1135,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1164,6 +1150,123 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128548833</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mölleskogen, Lången-området, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>511290</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6578077</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hovsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12974-2022 artfynd.xlsx
+++ b/artfynd/A 12974-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87069564</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111225026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1031,6 +1046,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126842634</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110839532</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,8 +1292,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128548833</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>